--- a/CAIP210.xlsx
+++ b/CAIP210.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moham\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E5CC4C-E126-499F-93BD-E2E299FFD3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12311CA-92A7-40B0-A147-D85CC0F5E0B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="12196" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2035,7 +2035,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
@@ -2316,6 +2316,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -15409,6 +15412,8 @@
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.06640625" customWidth="1"/>
     <col min="10" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15617,8 +15622,8 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" s="84"/>
-      <c r="B10" s="80"/>
-      <c r="C10" s="80"/>
+      <c r="B10" s="155"/>
+      <c r="C10" s="155"/>
       <c r="D10" s="79"/>
       <c r="E10" s="80"/>
       <c r="F10" s="80"/>
@@ -15632,8 +15637,8 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" s="84"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="80"/>
+      <c r="B11" s="155"/>
+      <c r="C11" s="155"/>
       <c r="D11" s="79"/>
       <c r="E11" s="80"/>
       <c r="F11" s="80"/>
